--- a/Semester Planner - 330.xlsx
+++ b/Semester Planner - 330.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">Input Start Info:</t>
   </si>
@@ -78,16 +78,31 @@
     <t xml:space="preserve">electric field, charge distributions</t>
   </si>
   <si>
+    <t xml:space="preserve">Homework catch up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electric field, volume integrals, and flux</t>
+  </si>
+  <si>
     <t xml:space="preserve">flux and gauss’s law</t>
   </si>
   <si>
+    <t xml:space="preserve">Exam 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">MID TERM GRADES</t>
   </si>
   <si>
+    <t xml:space="preserve">Exam 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">EASTER NO CLASS</t>
   </si>
   <si>
     <t xml:space="preserve">** SHORT WEEK **  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exam 3</t>
   </si>
   <si>
     <t xml:space="preserve">LAST WEEK OF CLASS</t>
@@ -760,7 +775,7 @@
       <c r="E18" s="22"/>
       <c r="F18" s="19"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="n">
         <v>3</v>
       </c>
@@ -771,7 +786,9 @@
         <f aca="false">IF(D18="",D17+IF(OR(WEEKDAY(D17)=2,WEEKDAY(D17)=4),2,3),"")</f>
         <v>44235</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="18" t="s">
+        <v>19</v>
+      </c>
       <c r="F19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -781,7 +798,7 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="16"/>
       <c r="C21" s="20" t="n">
         <v>8</v>
@@ -790,7 +807,9 @@
         <f aca="false">IF(D20="",D19+IF(OR(WEEKDAY(D19)=2,WEEKDAY(D19)=4),2,3),"")</f>
         <v>44237</v>
       </c>
-      <c r="E21" s="22"/>
+      <c r="E21" s="22" t="s">
+        <v>20</v>
+      </c>
       <c r="F21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -878,7 +897,7 @@
       <c r="E30" s="22"/>
       <c r="F30" s="19"/>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="16" t="n">
         <v>5</v>
       </c>
@@ -890,7 +909,9 @@
         <v>44249</v>
       </c>
       <c r="E31" s="18"/>
-      <c r="F31" s="24"/>
+      <c r="F31" s="24" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="16"/>
@@ -1072,7 +1093,7 @@
       </c>
       <c r="E49" s="18"/>
       <c r="F49" s="19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1120,7 +1141,7 @@
       <c r="E54" s="22"/>
       <c r="F54" s="19"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="16" t="n">
         <v>9</v>
       </c>
@@ -1132,7 +1153,9 @@
         <v>44277</v>
       </c>
       <c r="E55" s="18"/>
-      <c r="F55" s="19"/>
+      <c r="F55" s="19" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="16"/>
@@ -1254,10 +1277,10 @@
         <v>44291</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1305,7 +1328,7 @@
       <c r="E72" s="22"/>
       <c r="F72" s="19"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="16" t="n">
         <v>12</v>
       </c>
@@ -1317,7 +1340,9 @@
         <v>44298</v>
       </c>
       <c r="E73" s="18"/>
-      <c r="F73" s="19"/>
+      <c r="F73" s="19" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="16"/>
@@ -1436,7 +1461,7 @@
       </c>
       <c r="E85" s="18"/>
       <c r="F85" s="19" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1475,7 +1500,7 @@
         <v>44316</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F89" s="19"/>
     </row>
@@ -1503,7 +1528,7 @@
       </c>
       <c r="E91" s="18"/>
       <c r="F91" s="19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
